--- a/Lumbee_RIVR_Tech_IRU_Package/04_Financial_Model/Lumbee_RIVR_Tech_IRU_Financial_Model.xlsx
+++ b/Lumbee_RIVR_Tech_IRU_Package/04_Financial_Model/Lumbee_RIVR_Tech_IRU_Financial_Model.xlsx
@@ -13783,7 +13783,7 @@
     <row r="46">
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Reserved-capacity value to Tribe</t>
+          <t>Reserved-capacity value to Lumbee Tribe</t>
         </is>
       </c>
       <c r="C46" s="26" t="n">
